--- a/www/download/IND.gdp.s.du.WIOD16.xlsx
+++ b/www/download/IND.gdp.s.du.WIOD16.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>63954.2157091649</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>63389.7046115489</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>63684.3713954528</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>71549.637401466</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>78831.1204871772</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>88272.9624373194</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>96483.8950757847</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>113936.710678194</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>122161.429301366</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>114411.093167688</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>127788.485329718</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>139414.747065511</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>133008.681771031</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>137237.709270438</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>138300.862293857</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>25877.6696429959</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>25517.2355030102</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>25203.1358541118</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>27626.2068061319</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>30735.2980586415</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>32603.5335703096</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>34412.9479091808</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>39579.0268776343</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>43780.5287610595</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>38457.0597537</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>42671.8473495463</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>46025.6427764997</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>44612.275797453</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>44364.0752519976</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>44620.5259990725</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>21924.6094851666</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>21818.9192832021</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>21543.2807634001</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>23249.7636152927</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>25752.1767444459</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>27437.4085298572</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>29373.358273882</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>33601.3821964113</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>36864.5430221233</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>32780.4446253281</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>36462.8787571427</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>39737.4294373526</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>38671.5067070019</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>38393.0140594747</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>38579.6538504671</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>30467.6654595045</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>29810.0722541112</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>29980.5146588216</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>32479.1469631406</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>36183.6165598671</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>38773.4008632274</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>42491.063688631</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>49087.6587006809</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>56016.352437982</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>46888.0816944215</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>48272.9007581389</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>49745.9634484015</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>46747.2421367846</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>46461.0119165191</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>48661.79155594</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.707</t>
+          <t>706707.357803453</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>690322.268587989</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.723</t>
+          <t>722831.966955374</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.801</t>
+          <t>801399.748747405</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>930479.029791602</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1.017</t>
+          <t>1016624.90400767</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1.055</t>
+          <t>1054498.96203058</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>1.216</t>
+          <t>1216044.65016797</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>1.357</t>
+          <t>1357184.58431345</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1.217</t>
+          <t>1217008.95561091</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1.381</t>
+          <t>1381338.33098518</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1.463</t>
+          <t>1463353.14981366</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1.434</t>
+          <t>1434077.56890452</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>1.467</t>
+          <t>1466755.07438836</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>1.496</t>
+          <t>1496426.77565606</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>94781.9616415457</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>93999.9362783727</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>96177.4397385526</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>105257.797073038</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>118388.99694656</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>128366.833624921</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>137071.896086747</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>157061.519510516</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>0.174</t>
+          <t>173837.165757562</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>151010.000366869</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>171588.047649771</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>183699.139555982</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>185000.384017713</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>184823.957277773</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>0.194</t>
+          <t>194123.78014155</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8.083</t>
+          <t>8083617.22303388</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>8.028</t>
+          <t>8029299.30783722</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>8.209</t>
+          <t>8210660.86618096</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>8.803</t>
+          <t>8804209.10681044</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>9.754</t>
+          <t>9754538.54177619</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>10.459</t>
+          <t>10460168.129824</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>11.458</t>
+          <t>11457552.6941972</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>13.214</t>
+          <t>13215370.9033115</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>14.861</t>
+          <t>14861899.1241105</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>13.669</t>
+          <t>13669606.2868205</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>15.103</t>
+          <t>15105019.7029488</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>17.402</t>
+          <t>17404629.3221423</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>17.056</t>
+          <t>17057480.0132433</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>16.835</t>
+          <t>16835028.5110119</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>16.585</t>
+          <t>16584696.9405335</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1808.2765629951</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1814.3633585579</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1825.71192510738</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2206.85994569078</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2433.65069689645</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2647.36626476425</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2799.36855482388</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3263.58211002297</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3588.23652347749</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3259.801387122</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3453.26019187862</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3493.37672340677</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3176.52787864981</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2862.44198190458</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2743.39783769922</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>42381.057312552</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>39643.8688279002</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>39589.9756462459</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>42067.9442544613</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>47583.6759230206</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>52044.9158870251</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>54621.6852488517</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>62496.4542100022</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>68634.4150274227</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>59736.0975420007</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>66179.8971314147</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>71333.4319476936</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>69159.0522306562</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>68669.5762734488</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>69387.6473648566</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>221566.319461063</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.216</t>
+          <t>215618.106052969</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.214</t>
+          <t>213845.746208924</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0.228</t>
+          <t>228254.510179529</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0.251</t>
+          <t>251160.656858636</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>264599.363530532</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>0.284</t>
+          <t>283710.4393593</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>325036.396588857</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>356568.842599491</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>310273.834559639</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>352517.970401012</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>0.384</t>
+          <t>383728.966626648</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>0.376</t>
+          <t>375756.752131211</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>0.376</t>
+          <t>376007.896229232</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>0.384</t>
+          <t>384465.96361815</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>17571.4008402287</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>17564.8895990677</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>17454.061734434</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>18546.9477321114</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>20223.4237963941</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>21808.7818387638</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>23489.0840209087</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>26436.1922360352</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>28736.6835718399</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>25105.0496467329</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>26757.1262880672</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>28608.6026205058</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>27374.3778536699</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>27438.1381465454</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>27834.9829202821</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>117289.995997886</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>119402.278139821</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>122576.379495656</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>136984.589877568</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>153833.792779233</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>169225.869944801</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>182072.03499863</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>0.208</t>
+          <t>207726.623022127</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>218384.797042163</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>179260.62204961</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>0.192</t>
+          <t>191999.225598032</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>194690.684989907</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>176214.854104046</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>168464.527903777</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>170598.486703693</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5308.40833479195</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5331.39197654862</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5404.88270883111</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6232.35644548601</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6907.26574458633</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7459.77998058895</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8194.14621468463</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9367.03762958671</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9706.78396201707</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7301.45561533705</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7635.82638956698</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9215.02199225992</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8653.08283246573</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8407.95392289776</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8609.33186788789</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>17772.0258382872</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>17597.6820755566</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>17628.6935184932</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>18970.7096592787</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>20991.0917492891</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>22693.9169648703</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>24386.0421147086</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>27962.6145098693</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>30822.705796979</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>26683.4629215542</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>29483.3384616855</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>31755.3732004784</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>30870.2189751297</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>30243.9169889227</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>30048.3494192898</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>137899.718840695</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>136521.605314358</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>134011.350210612</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>145294.935346976</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>163751.781584447</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>176126.123467909</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>185258.434589264</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.214</t>
+          <t>213956.184029368</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>235038.784023304</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>209206.490198855</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.231</t>
+          <t>230992.437461723</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>246729.977114625</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>239264.767864521</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.236</t>
+          <t>236314.132944385</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>237217.330237337</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>163973.835392115</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>161062.222214282</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>161332.892670291</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.174</t>
+          <t>173656.106652977</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.191</t>
+          <t>191158.713886157</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>209962.730735755</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>223002.856231584</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.252</t>
+          <t>251905.311242619</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.271</t>
+          <t>270807.748424719</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>248966.313482853</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>276201.921819024</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>293466.330531524</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>0.292</t>
+          <t>292202.592424883</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>0.295</t>
+          <t>294751.535014853</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>303580.779905423</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>35211.2086133608</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>34307.8097994901</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>34234.0093277242</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>37292.0199171438</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>40505.8984520046</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>47195.2940028985</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>49509.662286524</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>56657.6731036148</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>61254.9889868296</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>55478.5945922978</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>54638.5159491973</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>52238.3918522686</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>46245.0922292278</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>44529.0929144363</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>44259.6001009634</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>42884.2898554268</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>41123.0580144139</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>41486.9060192493</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>43709.6425483492</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>47663.1384850289</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>49778.1996089882</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>52696.244355256</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>57628.2892775637</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>59583.9532169001</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>52964.3039782264</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>52013.3089393725</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>55778.0308112324</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>51833.388518636</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>50252.2997584965</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>52836.5565003522</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.835</t>
+          <t>834829.995590035</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>869770.257822491</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.923</t>
+          <t>922718.509098942</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1.062</t>
+          <t>1061799.35710637</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1.187</t>
+          <t>1187247.76292397</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1.157</t>
+          <t>1157416.40415052</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>1.139</t>
+          <t>1138890.50067918</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>1.316</t>
+          <t>1316241.6548182</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>1.438</t>
+          <t>1438157.1828379</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1.325</t>
+          <t>1325464.16300773</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1.524</t>
+          <t>1524196.54558201</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1.615</t>
+          <t>1615249.808886</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1.733</t>
+          <t>1732915.49925615</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>1.929</t>
+          <t>1929466.3139959</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2159883.59673246</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>6170638.53830434</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>6271196.53497809</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>6.479</t>
+          <t>6480532.15804475</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>7.251</t>
+          <t>7251998.80480274</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8250664.5885681</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>8.892</t>
+          <t>8892760.83854085</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>9.349</t>
+          <t>9349453.92957915</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>10.525</t>
+          <t>10526259.6361706</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>11.419</t>
+          <t>11420230.3700398</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>10.411</t>
+          <t>10411450.4526379</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>11.592</t>
+          <t>11592801.7218424</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>12.418</t>
+          <t>12419855.6758836</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>13.73</t>
+          <t>13731211.1786708</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>15.298</t>
+          <t>15298746.1192593</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>16.385</t>
+          <t>16384520.8325273</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>13968.7404072387</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>14237.4216704543</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>14226.3383920435</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>15565.5814247935</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>17773.1442662267</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>19884.037716655</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>21939.0909196775</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>25315.0952573931</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>26520.6977965</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>21113.0111001327</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>21805.1779932959</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>22637.3692975373</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>21625.6688281717</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>22657.6768292924</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>23332.7523788025</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>154049.315835451</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>154065.744538339</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>154501.27609476</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>167962.567309157</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>187746.751160567</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>0.201</t>
+          <t>201395.421903187</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>0.216</t>
+          <t>216244.162715631</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>246518.783314233</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>0.267</t>
+          <t>266724.065424825</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>228776.172941884</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>248878.757970612</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>0.264</t>
+          <t>263800.441865593</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>245408.441913052</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>236971.442808517</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>0.238</t>
+          <t>238014.691525358</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>0.506</t>
+          <t>505845.941175948</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.488</t>
+          <t>487804.437689952</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.475</t>
+          <t>475250.286230143</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>0.517</t>
+          <t>516797.798378507</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>571036.031645039</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>610328.028212833</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>0.652</t>
+          <t>652096.532066978</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>0.735</t>
+          <t>734941.662728097</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>0.782</t>
+          <t>782311.653243908</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>0.668</t>
+          <t>668076.528844512</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>0.753</t>
+          <t>752591.844308879</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>0.802</t>
+          <t>802221.649918326</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>0.787</t>
+          <t>786984.62388359</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>0.773</t>
+          <t>772947.00464581</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>0.762</t>
+          <t>762216.677100338</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>175707.591521358</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>172006.803662895</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>175796.842318076</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>0.194</t>
+          <t>194121.679437537</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>221671.884997925</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>0.228</t>
+          <t>228207.971961105</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>0.241</t>
+          <t>241137.869046166</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>265071.637088197</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>0.288</t>
+          <t>287724.699697573</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>0.278</t>
+          <t>277695.000789781</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>0.309</t>
+          <t>308759.200509567</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>0.327</t>
+          <t>327046.887285872</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>0.316</t>
+          <t>316032.7951076</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>0.335</t>
+          <t>335273.855735657</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>0.341</t>
+          <t>341422.111810701</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>14097.5543978534</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13391.8269841677</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>13522.8612794277</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>15470.3953875971</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>16218.0175396412</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18020.0207520215</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19117.1631066199</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>21174.5749854266</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>22026.8373726522</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>17213.9970644557</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18013.6714676081</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19141.1458006979</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>18970.1467306004</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>18782.9301057469</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19082.4923985814</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1488.78954899653</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1518.68791639784</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1556.95227135137</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1738.50867672795</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1970.14603697408</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2105.07571247687</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2285.50264408098</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2701.96947077254</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3029.352161023</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2654.42019017431</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3006.75596951628</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3277.09994751467</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3225.84213450183</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3242.01752749114</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3305.92164552696</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8832.80050004735</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9123.59990254398</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8990.05204197888</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9736.92276402634</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10110.6098542609</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10770.967647175</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12357.4578436105</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13408.4033529108</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>15071.4594295343</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10920.4194000782</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11131.141894591</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12341.7388526196</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12272.1084729564</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12367.9769807361</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12306.3648513607</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>356067.236738679</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.342</t>
+          <t>341727.527590508</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.339</t>
+          <t>339515.08907148</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>379640.200066852</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.443</t>
+          <t>443057.370787988</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.473</t>
+          <t>472982.937254972</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.525</t>
+          <t>524711.277317445</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.605</t>
+          <t>604706.435914779</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.666</t>
+          <t>666303.48444104</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.576</t>
+          <t>576037.504437638</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>649660.883022791</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.694</t>
+          <t>693873.44919053</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.695</t>
+          <t>695153.722952088</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.685</t>
+          <t>685129.438939247</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.696</t>
+          <t>695497.389678455</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1261.36966843059</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1161.94659100099</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1199.42176636655</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1288.71606525316</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1320.37405501025</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1494.67442763686</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1502.48306301345</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1753.33712943439</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2031.29926669505</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1900.29092468059</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2110.66199415365</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2077.28651774519</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1967.06313047167</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1985.09793796169</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1950.27954270454</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>40256.997865659</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>40405.5477342736</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>41004.3798801268</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>44409.9068408861</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>48646.0382513431</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>51850.8085051432</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>54963.5238743388</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>63183.4253585911</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>69925.6748551467</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>63276.9334677267</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>69302.4952113669</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>74284.8404818026</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>71616.2775106406</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>70780.0574436329</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>70280.1395939559</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>161153.44370596</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>162095.393084736</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>151339.922933047</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>163347.417560627</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>181921.183652177</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.198</t>
+          <t>198435.301477056</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.214</t>
+          <t>214248.538591939</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>247229.553947204</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.279</t>
+          <t>278855.194884229</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>246423.544552327</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>0.263</t>
+          <t>263094.018884809</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>0.279</t>
+          <t>279359.863489356</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>0.269</t>
+          <t>269362.521188002</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>270240.78471846</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>0.271</t>
+          <t>271017.93305235</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>46904.336844403</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>46421.5012028688</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>46148.8511267021</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>48947.2546962387</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>52687.1640130317</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>55237.4757415898</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>57621.8732153988</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>64441.3747336602</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>68492.8670922703</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>59945.3812936746</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>65059.3108015206</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>67084.9171044227</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>61904.2200643027</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>60586.7728548898</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>61821.2415871182</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>133652.171903351</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>131592.894273128</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>112222.330350992</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>0.126</t>
+          <t>125902.062967545</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>132402.122481561</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>141060.584945447</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>145296.972778647</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>164787.508305253</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>176547.439601239</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>154365.70462062</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>171885.917074101</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>182406.640622327</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>133807.08914686</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>132133.676611107</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>132837.000484056</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>0.782</t>
+          <t>781741.654652653</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>759927.691364473</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.761</t>
+          <t>760879.605698521</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>0.827</t>
+          <t>827338.399232127</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0.913</t>
+          <t>913445.51646786</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>0.985</t>
+          <t>984788.333133858</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>1.045</t>
+          <t>1045416.00945549</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>1.181</t>
+          <t>1181515.80536361</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>1.167</t>
+          <t>1166959.21906576</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>0.999</t>
+          <t>998675.210259065</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1.106</t>
+          <t>1106543.94807938</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>1.144</t>
+          <t>1144180.85354862</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1.138</t>
+          <t>1137791.31182203</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>1.082</t>
+          <t>1082145.97431977</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>1.048</t>
+          <t>1048165.79681284</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>17022.7379318303</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>16807.1416153691</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>16067.5858054835</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>16993.777100728</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19058.6894207715</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>20493.473179461</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>21669.44994424</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>24703.8904354529</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>27938.9880150613</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>23659.876453391</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>26393.6866517765</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>28151.3554698297</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>26902.9478792738</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>26476.4930973279</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>26825.4500467708</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7531.32586970554</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7327.81936172782</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7502.01029173195</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8065.92128709148</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9022.8940722117</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9454.01322095748</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9866.23673894746</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11319.2189188776</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>12687.5889865592</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11113.1512826489</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12091.1212898814</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12406.7664412843</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11696.7624597309</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11684.8401452409</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12038.1651398979</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>32258.0647309218</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>32104.8166873999</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>31967.6626972355</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>34258.7871993063</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>38102.2146965101</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>40697.6295930845</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>43212.4010863511</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>50015.0080916365</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>55116.5673253674</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>48368.7767067807</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>54374.5415865261</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>59109.7448116368</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>57334.3418009058</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>57263.3420313054</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>58197.7336913122</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0.251</t>
+          <t>251145.700777304</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>248825.454292676</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.233</t>
+          <t>232771.45720824</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>244624.953567379</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0.275</t>
+          <t>274734.222228747</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>0.291</t>
+          <t>290873.509809581</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>0.294</t>
+          <t>294299.705425955</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>0.312</t>
+          <t>312496.82376155</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>0.345</t>
+          <t>345503.978942933</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>0.308</t>
+          <t>308005.442998125</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>0.367</t>
+          <t>367390.890789957</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>0.417</t>
+          <t>417350.840863649</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>439911.373171987</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>0.472</t>
+          <t>472247.915088194</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>0.531</t>
+          <t>531421.39430471</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>151475.060911713</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>138982.733097682</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>148141.909586551</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>163950.3744072</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>185477.065370887</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>0.197</t>
+          <t>197232.996550673</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>214841.12721724</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>244869.625074003</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>0.259</t>
+          <t>259328.433899021</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>235352.600104369</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>276376.235195627</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>0.284</t>
+          <t>284425.378365254</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>0.281</t>
+          <t>281097.319579842</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>0.284</t>
+          <t>284148.386875558</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>0.292</t>
+          <t>291514.148173545</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>0.761</t>
+          <t>760952.404815262</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.744</t>
+          <t>744122.253229293</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.732</t>
+          <t>732180.449983501</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>0.788</t>
+          <t>788539.702634391</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0.882</t>
+          <t>882533.162814703</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>0.963</t>
+          <t>962687.215697882</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>1.044</t>
+          <t>1044163.51529475</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>1.194</t>
+          <t>1194489.32569586</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>1.279</t>
+          <t>1279583.92784469</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>1.084</t>
+          <t>1084388.96460571</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1199851.84341344</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>1.293</t>
+          <t>1292930.80299609</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1.287</t>
+          <t>1286992.34088124</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>1.309</t>
+          <t>1309178.72216031</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>1.351</t>
+          <t>1350493.35030832</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>12150718.566696</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>12.377</t>
+          <t>12378920.8293366</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>13.104</t>
+          <t>13106463.6180246</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>14.684</t>
+          <t>14685555.5993683</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>16.677</t>
+          <t>16678581.8681418</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>18.187</t>
+          <t>18188385.5277525</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>19.799</t>
+          <t>19799269.2348297</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>22.737</t>
+          <t>22740038.2652249</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>25.266</t>
+          <t>25268393.6572079</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>23.288</t>
+          <t>23288915.9234548</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>26.022</t>
+          <t>26024818.3016252</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>28.835</t>
+          <t>28839939.9413264</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>29.715</t>
+          <t>29717421.4605604</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>31.171</t>
+          <t>31171945.9154165</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>32.595</t>
+          <t>32595173.0464048</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>32.661</t>
+          <t>32661827.2967165</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>32.84</t>
+          <t>32845073.8416418</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>33.986</t>
+          <t>33991212.0334108</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>37.545</t>
+          <t>37548985.5301068</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>42.313</t>
+          <t>42316660.2635565</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>45.644</t>
+          <t>45648176.5922173</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>49.148</t>
+          <t>49147848.8324442</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>56.212</t>
+          <t>56218294.4290552</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>62.033</t>
+          <t>62038743.2480645</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>56.604</t>
+          <t>56605754.4836621</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>63.072</t>
+          <t>63078236.4344416</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>69.659</t>
+          <t>69671439.7597008</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>71.423</t>
+          <t>71429420.5306162</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>74.433</t>
+          <t>74434535.2953624</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>77.078</t>
+          <t>77077315.067112</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4337,84 +4342,84 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>15196.3550638555</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>14519.746402162</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>14624.4530036515</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>15740.8772070027</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18198.5002385541</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19426.2721027218</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>20686.37464113</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>23518.6248039974</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>26471.077340362</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>23445.5942705464</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>24913.1118875859</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>25646.7876121394</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>23551.8119089058</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>22768.5856934943</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>23155.0163414955</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4424,84 +4429,84 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>29312.5651794701</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>28505.5799769683</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>28168.8696326409</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>30652.8745962091</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>34429.1051249238</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>37335.7116102377</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>40163.0521594367</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>45920.7918960439</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>50471.1308959425</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>45485.2540757008</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>50937.5379981044</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>55497.969273437</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>54622.1477405925</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>54671.8372522741</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>55661.6160520689</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4511,84 +4516,84 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>14720.7962548799</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>14364.9309072171</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>14446.9555662583</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>15549.0600457969</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>17481.9644255899</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19061.8455335793</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>20770.0329726466</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>24553.7878118519</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>27464.7335173539</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>24632.2161640361</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>27232.0889875537</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>29496.9211982365</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>29293.1342005804</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>29687.251633319</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>30187.1684208163</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4600,7 +4605,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4612,7 +4617,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4624,7 +4629,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4636,7 +4641,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4648,7 +4653,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4695,6 +4700,11 @@
           <t>gdp.s.du</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4729,6 +4739,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>WIOD16</t>
